--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>79127</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411406</v>
+        <v>129411377</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>79127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523048</v>
+        <v>523143</v>
       </c>
       <c r="R4" t="n">
-        <v>6937993</v>
+        <v>6938086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411427</v>
+        <v>129411395</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,7 +1009,7 @@
         <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6937994</v>
+        <v>6938056</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411395</v>
+        <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R6" t="n">
-        <v>6938056</v>
+        <v>6938030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R7" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R10" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411402</v>
+        <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523080</v>
+        <v>523068</v>
       </c>
       <c r="R11" t="n">
-        <v>6938054</v>
+        <v>6938002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411386</v>
+        <v>129411382</v>
       </c>
       <c r="B13" t="n">
         <v>80146</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523046</v>
+        <v>523094</v>
       </c>
       <c r="R13" t="n">
-        <v>6938011</v>
+        <v>6938072</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411382</v>
+        <v>129411386</v>
       </c>
       <c r="B14" t="n">
         <v>80146</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523094</v>
+        <v>523046</v>
       </c>
       <c r="R14" t="n">
-        <v>6938072</v>
+        <v>6938011</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411404</v>
+        <v>129411420</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R16" t="n">
-        <v>6938008</v>
+        <v>6938066</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växtplats 16</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411420</v>
+        <v>129411404</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523118</v>
+        <v>523083</v>
       </c>
       <c r="R17" t="n">
-        <v>6938066</v>
+        <v>6938008</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Växtplats 16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411408</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523055</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,11 +2522,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2650,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411431</v>
+        <v>129411384</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523136</v>
+        <v>523080</v>
       </c>
       <c r="R22" t="n">
-        <v>6938051</v>
+        <v>6938039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2747,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2822,7 +2817,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411384</v>
+        <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523080</v>
+        <v>523098</v>
       </c>
       <c r="R24" t="n">
-        <v>6938039</v>
+        <v>6937990</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80175</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R31" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411398</v>
+        <v>129411393</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523124</v>
+        <v>523153</v>
       </c>
       <c r="R32" t="n">
-        <v>6938040</v>
+        <v>6938019</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3721,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3849,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411424</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523105</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938029</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3920,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3949,7 +3949,7 @@
         <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411409</v>
+        <v>129411396</v>
       </c>
       <c r="B37" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523068</v>
+        <v>523104</v>
       </c>
       <c r="R37" t="n">
-        <v>6937994</v>
+        <v>6938057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,11 +4221,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,32 +4247,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411396</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523104</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938057</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4323,6 +4318,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,32 +4349,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4454,7 +4454,7 @@
         <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>79127</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
         <v>129411395</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>80050</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R10" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1566,7 @@
         <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>80052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R12" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411382</v>
+        <v>129411386</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523094</v>
+        <v>523046</v>
       </c>
       <c r="R13" t="n">
-        <v>6938072</v>
+        <v>6938011</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411386</v>
+        <v>129411382</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523046</v>
+        <v>523094</v>
       </c>
       <c r="R14" t="n">
-        <v>6938011</v>
+        <v>6938072</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>129411375</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411420</v>
+        <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523118</v>
+        <v>523083</v>
       </c>
       <c r="R16" t="n">
-        <v>6938066</v>
+        <v>6938008</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Växtplats 16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411404</v>
+        <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R17" t="n">
-        <v>6938008</v>
+        <v>6938066</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växtplats 16</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411431</v>
+        <v>129411384</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523136</v>
+        <v>523080</v>
       </c>
       <c r="R21" t="n">
-        <v>6938051</v>
+        <v>6938039</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411384</v>
+        <v>129411378</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523080</v>
+        <v>523153</v>
       </c>
       <c r="R22" t="n">
-        <v>6938039</v>
+        <v>6938019</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2745,7 +2745,7 @@
         <v>129411408</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R25" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>80177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3114,11 +3119,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R31" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411393</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,21 +3661,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523153</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938019</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411430</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523138</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938048</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411410</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523076</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411422</v>
+        <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523083</v>
+        <v>523104</v>
       </c>
       <c r="R36" t="n">
-        <v>6938064</v>
+        <v>6938057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,11 +4119,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411396</v>
+        <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523104</v>
+        <v>523083</v>
       </c>
       <c r="R37" t="n">
-        <v>6938057</v>
+        <v>6938064</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,6 +4216,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4247,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411399</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523118</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6938019</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4352,7 +4352,7 @@
         <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,11 +4920,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R45" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5022,6 +5017,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411406</v>
       </c>
       <c r="B3" t="n">
-        <v>79129</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523048</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411395</v>
+        <v>129411427</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,7 +1014,7 @@
         <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6938056</v>
+        <v>6937994</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411425</v>
+        <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938030</v>
+        <v>6938056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411406</v>
+        <v>129411425</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523048</v>
+        <v>523062</v>
       </c>
       <c r="R7" t="n">
-        <v>6937993</v>
+        <v>6938030</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411431</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523136</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6938051</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411384</v>
+        <v>129411408</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523080</v>
+        <v>523055</v>
       </c>
       <c r="R21" t="n">
-        <v>6938039</v>
+        <v>6937994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2661,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R22" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2742,32 +2747,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411384</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523080</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6938039</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2813,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411410</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523076</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938008</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411393</v>
+        <v>129411398</v>
       </c>
       <c r="B31" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523153</v>
+        <v>523124</v>
       </c>
       <c r="R31" t="n">
-        <v>6938019</v>
+        <v>6938040</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,6 +3624,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411421</v>
       </c>
       <c r="B32" t="n">
         <v>79043</v>
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523127</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938025</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3721,6 +3726,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,32 +3854,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411410</v>
+        <v>129411430</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523076</v>
+        <v>523138</v>
       </c>
       <c r="R34" t="n">
-        <v>6938008</v>
+        <v>6938048</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3915,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411398</v>
+        <v>129411424</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523124</v>
+        <v>523105</v>
       </c>
       <c r="R35" t="n">
-        <v>6938040</v>
+        <v>6938029</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4017,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411406</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>79130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523048</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937993</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>79129</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R5" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1076,7 +1071,7 @@
         <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R7" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411402</v>
+        <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523080</v>
+        <v>523068</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R11" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80052</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>129411386</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129411382</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129411375</v>
       </c>
       <c r="B15" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411408</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523055</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6937994</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R21" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2623,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,7 +2658,7 @@
         <v>129411431</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411384</v>
+        <v>129411378</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2782,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523080</v>
+        <v>523153</v>
       </c>
       <c r="R23" t="n">
-        <v>6938039</v>
+        <v>6938019</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2844,32 +2849,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R24" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>80178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80177</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411410</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523076</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938008</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411398</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523124</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938040</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3655,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411421</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523127</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938025</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3726,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411398</v>
       </c>
       <c r="B33" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523124</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938040</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3828,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411430</v>
+        <v>129411410</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523138</v>
+        <v>523076</v>
       </c>
       <c r="R34" t="n">
-        <v>6938048</v>
+        <v>6938008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3925,6 +3920,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R35" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411396</v>
+        <v>129411400</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523104</v>
+        <v>523094</v>
       </c>
       <c r="R36" t="n">
-        <v>6938057</v>
+        <v>6938031</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,6 +4119,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4145,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R37" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4220,7 +4225,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4250,7 +4255,7 @@
         <v>129411399</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4349,32 +4354,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411396</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523104</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938057</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4420,11 +4425,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R40" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4556,7 +4556,7 @@
         <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411425</v>
+        <v>129411427</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6938030</v>
+        <v>6937994</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411395</v>
+        <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R6" t="n">
-        <v>6938056</v>
+        <v>6938030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411408</v>
+        <v>129411384</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523055</v>
+        <v>523080</v>
       </c>
       <c r="R20" t="n">
-        <v>6937994</v>
+        <v>6938039</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,11 +2522,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R21" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2628,7 +2623,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411431</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523136</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6938051</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2726,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411384</v>
+        <v>129411431</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523080</v>
+        <v>523136</v>
       </c>
       <c r="R24" t="n">
-        <v>6938039</v>
+        <v>6938051</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>80178</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R25" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>80178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3114,11 +3119,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411393</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523153</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938019</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,7 +3548,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411430</v>
+        <v>129411421</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523138</v>
+        <v>523127</v>
       </c>
       <c r="R31" t="n">
-        <v>6938048</v>
+        <v>6938025</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,6 +3619,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411424</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523105</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938029</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411398</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523124</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938040</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3924,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411393</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523153</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938019</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4022,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411400</v>
+        <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523094</v>
+        <v>523104</v>
       </c>
       <c r="R36" t="n">
-        <v>6938031</v>
+        <v>6938057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,11 +4119,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4145,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411409</v>
+        <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523068</v>
+        <v>523083</v>
       </c>
       <c r="R37" t="n">
-        <v>6937994</v>
+        <v>6938064</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4225,7 +4220,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4349,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411396</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523104</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938057</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4425,6 +4420,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411422</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6938064</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411384</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523080</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6938039</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411408</v>
+        <v>129411384</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523055</v>
+        <v>523080</v>
       </c>
       <c r="R21" t="n">
-        <v>6937994</v>
+        <v>6938039</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2650,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411431</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523136</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6938051</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,11 +2716,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411378</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523153</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6938019</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2823,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411431</v>
+        <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523136</v>
+        <v>523098</v>
       </c>
       <c r="R24" t="n">
-        <v>6938051</v>
+        <v>6937990</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2949,7 +2949,7 @@
         <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411395</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>79130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6938056</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B4" t="n">
-        <v>79130</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411384</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523080</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6938039</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411431</v>
+        <v>129411384</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523136</v>
+        <v>523080</v>
       </c>
       <c r="R22" t="n">
-        <v>6938051</v>
+        <v>6938039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411393</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523153</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938019</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3548,7 +3553,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411421</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523127</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938025</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3619,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411396</v>
+        <v>129411422</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523104</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6938057</v>
+        <v>6938064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,6 +4119,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4145,10 +4150,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411422</v>
+        <v>129411396</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4156,21 +4161,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523083</v>
+        <v>523104</v>
       </c>
       <c r="R37" t="n">
-        <v>6938064</v>
+        <v>6938057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4216,11 +4221,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411399</v>
       </c>
       <c r="B39" t="n">
         <v>98724</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523118</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411409</v>
       </c>
       <c r="B40" t="n">
         <v>98724</v>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523068</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6937994</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>80178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80178</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411406</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523048</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411395</v>
+        <v>129411377</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>79130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R4" t="n">
-        <v>6938056</v>
+        <v>6938086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411425</v>
+        <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938030</v>
+        <v>6938056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411406</v>
+        <v>129411425</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523048</v>
+        <v>523062</v>
       </c>
       <c r="R7" t="n">
-        <v>6937993</v>
+        <v>6938030</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411431</v>
+        <v>129411384</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523136</v>
+        <v>523080</v>
       </c>
       <c r="R21" t="n">
-        <v>6938051</v>
+        <v>6938039</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411384</v>
+        <v>129411408</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523080</v>
+        <v>523055</v>
       </c>
       <c r="R22" t="n">
-        <v>6938039</v>
+        <v>6937994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,6 +2716,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2817,7 +2822,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2849,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411412</v>
+        <v>129411378</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523098</v>
+        <v>523153</v>
       </c>
       <c r="R24" t="n">
-        <v>6937990</v>
+        <v>6938019</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,7 +3046,7 @@
         <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411398</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523124</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938040</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411430</v>
+        <v>129411410</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523138</v>
+        <v>523076</v>
       </c>
       <c r="R31" t="n">
-        <v>6938048</v>
+        <v>6938008</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,6 +3624,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411424</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523105</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938029</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3752,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3763,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411421</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523127</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938025</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411393</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523153</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938019</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4017,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411422</v>
+        <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523083</v>
+        <v>523104</v>
       </c>
       <c r="R36" t="n">
-        <v>6938064</v>
+        <v>6938057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,11 +4119,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411396</v>
+        <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523104</v>
+        <v>523083</v>
       </c>
       <c r="R37" t="n">
-        <v>6938057</v>
+        <v>6938064</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,6 +4216,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4250,7 +4250,7 @@
         <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411399</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523118</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938019</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,10 +4451,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411409</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523068</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,11 +4920,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R45" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5022,6 +5017,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411406</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>79130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523048</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937993</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>79130</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411427</v>
+        <v>129411395</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,7 +1009,7 @@
         <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6937994</v>
+        <v>6938056</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411395</v>
+        <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R6" t="n">
-        <v>6938056</v>
+        <v>6938030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R7" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411388</v>
+        <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523068</v>
+        <v>523080</v>
       </c>
       <c r="R10" t="n">
-        <v>6938002</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411379</v>
+        <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523079</v>
+        <v>523068</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R12" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
         <v>98727</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,7 +2747,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
         <v>98727</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411398</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523124</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938040</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411410</v>
+        <v>129411393</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523076</v>
+        <v>523153</v>
       </c>
       <c r="R31" t="n">
-        <v>6938008</v>
+        <v>6938019</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411421</v>
+        <v>129411410</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523127</v>
+        <v>523076</v>
       </c>
       <c r="R34" t="n">
-        <v>6938025</v>
+        <v>6938008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3924,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411393</v>
+        <v>129411398</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523153</v>
+        <v>523124</v>
       </c>
       <c r="R35" t="n">
-        <v>6938019</v>
+        <v>6938040</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4022,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411399</v>
       </c>
       <c r="B38" t="n">
         <v>98727</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523118</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6938019</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411425</v>
+        <v>129411377</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523062</v>
+        <v>523143</v>
       </c>
       <c r="R6" t="n">
-        <v>6938030</v>
+        <v>6938086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411402</v>
+        <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523080</v>
+        <v>523068</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R11" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80053</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411431</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523136</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6938051</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411384</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523080</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6938039</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,11 +2716,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411378</v>
+        <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523153</v>
+        <v>523098</v>
       </c>
       <c r="R24" t="n">
-        <v>6938019</v>
+        <v>6937990</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R25" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3114,11 +3119,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411393</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523153</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938019</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
         <v>98727</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,7 +3946,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411398</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523124</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938040</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411396</v>
+        <v>129411422</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523104</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6938057</v>
+        <v>6938064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,6 +4119,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4145,10 +4150,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411422</v>
+        <v>129411396</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4156,21 +4161,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523083</v>
+        <v>523104</v>
       </c>
       <c r="R37" t="n">
-        <v>6938064</v>
+        <v>6938057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4216,11 +4221,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
         <v>98727</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411400</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523094</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6938031</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411425</v>
+        <v>129411395</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938030</v>
+        <v>6938056</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411395</v>
+        <v>129411427</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
         <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6938056</v>
+        <v>6937994</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411377</v>
+        <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523143</v>
+        <v>523062</v>
       </c>
       <c r="R6" t="n">
-        <v>6938086</v>
+        <v>6938030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411431</v>
+        <v>129411408</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523136</v>
+        <v>523055</v>
       </c>
       <c r="R21" t="n">
-        <v>6938051</v>
+        <v>6937994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411384</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523080</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6938039</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411431</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523136</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6938051</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2813,11 +2823,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2849,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R24" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411398</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523124</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938040</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411430</v>
+        <v>129411410</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523138</v>
+        <v>523076</v>
       </c>
       <c r="R31" t="n">
-        <v>6938048</v>
+        <v>6938008</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,6 +3624,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411424</v>
+        <v>129411421</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523105</v>
+        <v>523127</v>
       </c>
       <c r="R32" t="n">
-        <v>6938029</v>
+        <v>6938025</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3721,6 +3726,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411430</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523138</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938048</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,32 +3854,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411424</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523105</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938029</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3915,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411393</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523153</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938019</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4017,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R5" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411425</v>
+        <v>129411427</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938030</v>
+        <v>6937994</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411388</v>
+        <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523068</v>
+        <v>523080</v>
       </c>
       <c r="R10" t="n">
-        <v>6938002</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411379</v>
+        <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523079</v>
+        <v>523068</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R12" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411404</v>
+        <v>129411420</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R16" t="n">
-        <v>6938008</v>
+        <v>6938066</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växtplats 16</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411420</v>
+        <v>129411404</v>
       </c>
       <c r="B17" t="n">
         <v>98727</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523118</v>
+        <v>523083</v>
       </c>
       <c r="R17" t="n">
-        <v>6938066</v>
+        <v>6938008</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Växtplats 16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411412</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523098</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6937990</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2650,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411378</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523153</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6938019</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411421</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523127</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938025</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3726,11 +3726,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,7 +3752,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411430</v>
+        <v>129411421</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3792,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523138</v>
+        <v>523127</v>
       </c>
       <c r="R33" t="n">
-        <v>6938048</v>
+        <v>6938025</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3828,6 +3823,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,21 +3865,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R34" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R35" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411422</v>
+        <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523083</v>
+        <v>523104</v>
       </c>
       <c r="R36" t="n">
-        <v>6938064</v>
+        <v>6938057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,11 +4119,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,10 +4145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411396</v>
+        <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,21 +4156,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523104</v>
+        <v>523083</v>
       </c>
       <c r="R37" t="n">
-        <v>6938057</v>
+        <v>6938064</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,6 +4216,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411409</v>
       </c>
       <c r="B38" t="n">
         <v>98727</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523068</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6937994</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411400</v>
       </c>
       <c r="B39" t="n">
         <v>98727</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523094</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938031</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,11 +4920,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R45" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5022,6 +5017,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R5" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411406</v>
+        <v>129411425</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523048</v>
+        <v>523062</v>
       </c>
       <c r="R7" t="n">
-        <v>6937993</v>
+        <v>6938030</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411402</v>
+        <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523080</v>
+        <v>523068</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R11" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80053</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411420</v>
+        <v>129411404</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523118</v>
+        <v>523083</v>
       </c>
       <c r="R16" t="n">
-        <v>6938066</v>
+        <v>6938008</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Växtplats 16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411404</v>
+        <v>129411420</v>
       </c>
       <c r="B17" t="n">
         <v>98727</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R17" t="n">
-        <v>6938008</v>
+        <v>6938066</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växtplats 16</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411412</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523098</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6937990</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,11 +2522,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411408</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523055</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6937994</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2624,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411378</v>
+        <v>129411384</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2666,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523153</v>
+        <v>523080</v>
       </c>
       <c r="R22" t="n">
-        <v>6938019</v>
+        <v>6938039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2752,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411431</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523136</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6938051</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2823,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411384</v>
+        <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523080</v>
+        <v>523098</v>
       </c>
       <c r="R24" t="n">
-        <v>6938039</v>
+        <v>6937990</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411398</v>
+        <v>129411393</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523124</v>
+        <v>523153</v>
       </c>
       <c r="R30" t="n">
-        <v>6938040</v>
+        <v>6938019</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411410</v>
+        <v>129411421</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523076</v>
+        <v>523127</v>
       </c>
       <c r="R31" t="n">
-        <v>6938008</v>
+        <v>6938025</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3628,7 +3623,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3752,7 +3747,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411421</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3787,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523127</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938025</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3823,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411393</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523153</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938019</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3925,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411424</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523105</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938029</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4022,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411409</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
         <v>98727</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523068</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6937994</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411400</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
         <v>98727</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523094</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938031</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411395</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938056</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411406</v>
+        <v>129411425</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523048</v>
+        <v>523062</v>
       </c>
       <c r="R5" t="n">
-        <v>6937993</v>
+        <v>6938030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R6" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R7" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129411386</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129411382</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129411375</v>
       </c>
       <c r="B15" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411431</v>
+        <v>129411412</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523136</v>
+        <v>523098</v>
       </c>
       <c r="R21" t="n">
-        <v>6938051</v>
+        <v>6937990</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411384</v>
+        <v>129411408</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523080</v>
+        <v>523055</v>
       </c>
       <c r="R22" t="n">
-        <v>6938039</v>
+        <v>6937994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411378</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523153</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2813,11 +2823,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2849,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R24" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2949,7 +2949,7 @@
         <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>129411393</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>129411421</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129411430</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411410</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523076</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4051,7 +4051,7 @@
         <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411399</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523118</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6938019</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4352,7 +4352,7 @@
         <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4556,7 +4556,7 @@
         <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411395</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,7 +815,7 @@
         <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938056</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411395</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938056</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>80204</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R25" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>80204</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3114,11 +3119,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411393</v>
+        <v>129411410</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523153</v>
+        <v>523076</v>
       </c>
       <c r="R30" t="n">
-        <v>6938019</v>
+        <v>6938008</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411421</v>
+        <v>129411398</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523127</v>
+        <v>523124</v>
       </c>
       <c r="R31" t="n">
-        <v>6938025</v>
+        <v>6938040</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3623,7 +3628,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411393</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523153</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938019</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,7 +3752,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411421</v>
       </c>
       <c r="B33" t="n">
         <v>79070</v>
@@ -3782,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523127</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938025</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3818,6 +3823,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,32 +3854,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411410</v>
+        <v>129411430</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523076</v>
+        <v>523138</v>
       </c>
       <c r="R34" t="n">
-        <v>6938008</v>
+        <v>6938048</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3915,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411398</v>
+        <v>129411424</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523124</v>
+        <v>523105</v>
       </c>
       <c r="R35" t="n">
-        <v>6938040</v>
+        <v>6938029</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4017,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411395</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938056</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
         <v>129411425</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>79156</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411388</v>
+        <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523068</v>
+        <v>523080</v>
       </c>
       <c r="R10" t="n">
-        <v>6938002</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411379</v>
+        <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523079</v>
+        <v>523068</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>80084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R12" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411386</v>
+        <v>129411375</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>80209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523046</v>
+        <v>523153</v>
       </c>
       <c r="R13" t="n">
-        <v>6938011</v>
+        <v>6938019</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411382</v>
+        <v>129411386</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523094</v>
+        <v>523046</v>
       </c>
       <c r="R14" t="n">
-        <v>6938072</v>
+        <v>6938011</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129411375</v>
+        <v>129411382</v>
       </c>
       <c r="B15" t="n">
-        <v>80204</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523153</v>
+        <v>523094</v>
       </c>
       <c r="R15" t="n">
-        <v>6938019</v>
+        <v>6938072</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R21" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,7 +2648,7 @@
         <v>129411408</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,32 +2747,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411378</v>
+        <v>129411412</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523153</v>
+        <v>523098</v>
       </c>
       <c r="R23" t="n">
-        <v>6938019</v>
+        <v>6937990</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2823,6 +2818,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411384</v>
+        <v>129411378</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>80181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523080</v>
+        <v>523153</v>
       </c>
       <c r="R24" t="n">
-        <v>6938039</v>
+        <v>6938019</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2949,7 +2949,7 @@
         <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411410</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523076</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938008</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411398</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523124</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938040</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3655,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3661,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3752,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411421</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3787,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523127</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938025</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3823,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411430</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523138</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938048</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3925,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411424</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523105</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938029</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4022,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411396</v>
+        <v>129411400</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523104</v>
+        <v>523094</v>
       </c>
       <c r="R36" t="n">
-        <v>6938057</v>
+        <v>6938031</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,6 +4119,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4145,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R37" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4220,7 +4225,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4250,7 +4255,7 @@
         <v>129411399</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4349,32 +4354,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411396</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523104</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938057</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4420,11 +4425,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R40" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>79161</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411425</v>
+        <v>129411377</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523062</v>
+        <v>523143</v>
       </c>
       <c r="R5" t="n">
-        <v>6938030</v>
+        <v>6938086</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1071,7 @@
         <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411375</v>
+        <v>129411386</v>
       </c>
       <c r="B13" t="n">
-        <v>80209</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523153</v>
+        <v>523046</v>
       </c>
       <c r="R13" t="n">
-        <v>6938019</v>
+        <v>6938011</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411386</v>
+        <v>129411382</v>
       </c>
       <c r="B14" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523046</v>
+        <v>523094</v>
       </c>
       <c r="R14" t="n">
-        <v>6938011</v>
+        <v>6938072</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129411382</v>
+        <v>129411375</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523094</v>
+        <v>523153</v>
       </c>
       <c r="R15" t="n">
-        <v>6938072</v>
+        <v>6938019</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411384</v>
+        <v>129411408</v>
       </c>
       <c r="B21" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523080</v>
+        <v>523055</v>
       </c>
       <c r="R21" t="n">
-        <v>6938039</v>
+        <v>6937994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2720,7 +2725,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411412</v>
+        <v>129411378</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>80182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2782,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523098</v>
+        <v>523153</v>
       </c>
       <c r="R23" t="n">
-        <v>6937990</v>
+        <v>6938019</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2818,11 +2823,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,7 +2849,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411378</v>
+        <v>129411384</v>
       </c>
       <c r="B24" t="n">
         <v>80181</v>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523153</v>
+        <v>523080</v>
       </c>
       <c r="R24" t="n">
-        <v>6938019</v>
+        <v>6938039</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2949,7 +2949,7 @@
         <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129411424</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411409</v>
+        <v>129411396</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523068</v>
+        <v>523104</v>
       </c>
       <c r="R37" t="n">
-        <v>6937994</v>
+        <v>6938057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,11 +4221,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4349,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411396</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523104</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938057</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4425,6 +4420,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411422</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6938064</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411402</v>
+        <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523080</v>
+        <v>523068</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>80085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R11" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80085</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411422</v>
+        <v>129411400</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523083</v>
+        <v>523094</v>
       </c>
       <c r="R36" t="n">
-        <v>6938064</v>
+        <v>6938031</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411396</v>
+        <v>129411409</v>
       </c>
       <c r="B37" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523104</v>
+        <v>523068</v>
       </c>
       <c r="R37" t="n">
-        <v>6938057</v>
+        <v>6937994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,6 +4221,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4247,7 +4252,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411399</v>
       </c>
       <c r="B38" t="n">
         <v>98769</v>
@@ -4282,10 +4287,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523118</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6938019</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4327,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,32 +4354,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411422</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523083</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938064</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4456,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411396</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523104</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6938057</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4522,11 +4527,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R3" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411425</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6938030</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B5" t="n">
-        <v>79162</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R5" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411395</v>
+        <v>129411425</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R6" t="n">
-        <v>6938056</v>
+        <v>6938030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,7 +1168,7 @@
         <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411426</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129411386</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129411382</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129411375</v>
       </c>
       <c r="B15" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129411392</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411431</v>
+        <v>129411408</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523136</v>
+        <v>523055</v>
       </c>
       <c r="R20" t="n">
-        <v>6938051</v>
+        <v>6937994</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R21" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2623,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2650,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411378</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>80187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523153</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6938019</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B23" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R23" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2852,7 +2852,7 @@
         <v>129411384</v>
       </c>
       <c r="B24" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411430</v>
+        <v>129411393</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523138</v>
+        <v>523153</v>
       </c>
       <c r="R31" t="n">
-        <v>6938048</v>
+        <v>6938019</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411424</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523105</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938029</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3847,7 +3847,7 @@
         <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411400</v>
+        <v>129411396</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523094</v>
+        <v>523104</v>
       </c>
       <c r="R36" t="n">
-        <v>6938031</v>
+        <v>6938057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,11 +4119,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4145,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411409</v>
+        <v>129411422</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523068</v>
+        <v>523083</v>
       </c>
       <c r="R37" t="n">
-        <v>6937994</v>
+        <v>6938064</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4225,7 +4220,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4349,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4429,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4456,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411396</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523104</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6938057</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4527,6 +4522,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4556,7 +4556,7 @@
         <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>129411394</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,11 +4920,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R45" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5022,6 +5017,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5051,7 +5051,7 @@
         <v>129411389</v>
       </c>
       <c r="B46" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411425</v>
+        <v>129411377</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523062</v>
+        <v>523143</v>
       </c>
       <c r="R6" t="n">
-        <v>6938030</v>
+        <v>6938086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411408</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>80187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523055</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2522,11 +2522,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R21" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2624,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411378</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
-        <v>80187</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523153</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6938019</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2726,6 +2716,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2747,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411431</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523136</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6938051</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2823,6 +2818,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411384</v>
+        <v>129411431</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523080</v>
+        <v>523136</v>
       </c>
       <c r="R24" t="n">
-        <v>6938039</v>
+        <v>6938051</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411430</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523138</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938048</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,10 +3548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3559,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R31" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,7 +3645,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411421</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523127</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938025</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411410</v>
       </c>
       <c r="B34" t="n">
         <v>98774</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523076</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,7 +3946,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B35" t="n">
         <v>98774</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4145,32 +4145,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R37" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4247,32 +4247,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R38" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411409</v>
+        <v>129411400</v>
       </c>
       <c r="B39" t="n">
         <v>98774</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523068</v>
+        <v>523094</v>
       </c>
       <c r="R39" t="n">
-        <v>6937994</v>
+        <v>6938031</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 12</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411427</v>
+        <v>129411406</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523048</v>
       </c>
       <c r="R3" t="n">
-        <v>6937994</v>
+        <v>6937993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411395</v>
+        <v>129411377</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R5" t="n">
-        <v>6938056</v>
+        <v>6938086</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411377</v>
+        <v>129411427</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938086</v>
+        <v>6937994</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411406</v>
+        <v>129411395</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523048</v>
+        <v>523103</v>
       </c>
       <c r="R7" t="n">
-        <v>6937993</v>
+        <v>6938056</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411388</v>
+        <v>129411402</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523068</v>
+        <v>523080</v>
       </c>
       <c r="R10" t="n">
-        <v>6938002</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411379</v>
+        <v>129411388</v>
       </c>
       <c r="B11" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523079</v>
+        <v>523068</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>80090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R12" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B22" t="n">
         <v>98774</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,7 +2747,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411412</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523098</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6937990</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växtplats 13</t>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411430</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523138</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938048</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3522,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3548,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3559,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R31" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3645,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411421</v>
+        <v>129411430</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523127</v>
+        <v>523138</v>
       </c>
       <c r="R32" t="n">
-        <v>6938025</v>
+        <v>6938048</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411424</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523105</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938029</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411410</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
         <v>98774</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523076</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938008</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 11</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,7 +3946,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411398</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
         <v>98774</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523124</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938040</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411396</v>
+        <v>129411400</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523104</v>
+        <v>523094</v>
       </c>
       <c r="R36" t="n">
-        <v>6938057</v>
+        <v>6938031</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4119,6 +4119,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,32 +4252,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411422</v>
+        <v>129411399</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4282,10 +4287,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523083</v>
+        <v>523118</v>
       </c>
       <c r="R38" t="n">
-        <v>6938064</v>
+        <v>6938019</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4322,7 +4327,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4349,32 +4354,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R39" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,32 +4456,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411399</v>
+        <v>129411396</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4486,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523118</v>
+        <v>523104</v>
       </c>
       <c r="R40" t="n">
-        <v>6938019</v>
+        <v>6938057</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4522,11 +4527,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,11 +4920,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R45" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5022,6 +5017,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411406</v>
+        <v>129411395</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523048</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6937993</v>
+        <v>6938056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411425</v>
+        <v>129411406</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523062</v>
+        <v>523048</v>
       </c>
       <c r="R4" t="n">
-        <v>6938030</v>
+        <v>6937993</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411395</v>
+        <v>129411425</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R7" t="n">
-        <v>6938056</v>
+        <v>6938030</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411402</v>
+        <v>129411379</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>80090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523080</v>
+        <v>523079</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129411379</v>
+        <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523079</v>
+        <v>523080</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411384</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523080</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6938039</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411408</v>
+        <v>129411384</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523055</v>
+        <v>523080</v>
       </c>
       <c r="R22" t="n">
-        <v>6937994</v>
+        <v>6938039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,11 +2716,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,7 +2742,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -2782,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R23" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2822,7 +2817,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411431</v>
+        <v>129411412</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523136</v>
+        <v>523098</v>
       </c>
       <c r="R24" t="n">
-        <v>6938051</v>
+        <v>6937990</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411393</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523153</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938019</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411430</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523138</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938048</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411424</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523105</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938029</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,32 +4048,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411400</v>
+        <v>129411422</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523094</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6938031</v>
+        <v>6938064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växtplats 19</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4150,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411409</v>
+        <v>129411396</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523068</v>
+        <v>523104</v>
       </c>
       <c r="R37" t="n">
-        <v>6937994</v>
+        <v>6938057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4221,11 +4221,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411399</v>
+        <v>129411400</v>
       </c>
       <c r="B38" t="n">
         <v>98774</v>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523118</v>
+        <v>523094</v>
       </c>
       <c r="R38" t="n">
-        <v>6938019</v>
+        <v>6938031</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt Växtplats 20</t>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4349,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411422</v>
+        <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523083</v>
+        <v>523068</v>
       </c>
       <c r="R39" t="n">
-        <v>6938064</v>
+        <v>6937994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4429,7 +4424,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4456,32 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411396</v>
+        <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523104</v>
+        <v>523118</v>
       </c>
       <c r="R40" t="n">
-        <v>6938057</v>
+        <v>6938019</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4527,6 +4522,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt Växtplats 20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411383</v>
+        <v>129411423</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523075</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6938053</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4920,6 +4920,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411423</v>
+        <v>129411383</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523142</v>
+        <v>523075</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938053</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5017,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411395</v>
+        <v>129411406</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523103</v>
+        <v>523048</v>
       </c>
       <c r="R3" t="n">
-        <v>6938056</v>
+        <v>6937993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411406</v>
+        <v>129411427</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523048</v>
+        <v>523103</v>
       </c>
       <c r="R4" t="n">
-        <v>6937993</v>
+        <v>6937994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411377</v>
+        <v>129411425</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523143</v>
+        <v>523062</v>
       </c>
       <c r="R5" t="n">
-        <v>6938086</v>
+        <v>6938030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411427</v>
+        <v>129411377</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523103</v>
+        <v>523143</v>
       </c>
       <c r="R6" t="n">
-        <v>6937994</v>
+        <v>6938086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411425</v>
+        <v>129411395</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523062</v>
+        <v>523103</v>
       </c>
       <c r="R7" t="n">
-        <v>6938030</v>
+        <v>6938056</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411379</v>
+        <v>129411388</v>
       </c>
       <c r="B10" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523079</v>
+        <v>523068</v>
       </c>
       <c r="R10" t="n">
-        <v>6938003</v>
+        <v>6938002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129411388</v>
+        <v>129411379</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523068</v>
+        <v>523079</v>
       </c>
       <c r="R11" t="n">
-        <v>6938002</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411378</v>
+        <v>129411431</v>
       </c>
       <c r="B20" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523153</v>
+        <v>523136</v>
       </c>
       <c r="R20" t="n">
-        <v>6938019</v>
+        <v>6938051</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411431</v>
+        <v>129411408</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523136</v>
+        <v>523055</v>
       </c>
       <c r="R21" t="n">
-        <v>6938051</v>
+        <v>6937994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411384</v>
+        <v>129411412</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523080</v>
+        <v>523098</v>
       </c>
       <c r="R22" t="n">
-        <v>6938039</v>
+        <v>6937990</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2716,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411408</v>
+        <v>129411378</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>80187</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523055</v>
+        <v>523153</v>
       </c>
       <c r="R23" t="n">
-        <v>6937994</v>
+        <v>6938019</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2813,11 +2823,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2849,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129411412</v>
+        <v>129411384</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523098</v>
+        <v>523080</v>
       </c>
       <c r="R24" t="n">
-        <v>6937990</v>
+        <v>6938039</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B25" t="n">
-        <v>80215</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R25" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3114,11 +3119,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411421</v>
+        <v>129411398</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523127</v>
+        <v>523124</v>
       </c>
       <c r="R30" t="n">
-        <v>6938025</v>
+        <v>6938040</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411430</v>
+        <v>129411410</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523138</v>
+        <v>523076</v>
       </c>
       <c r="R31" t="n">
-        <v>6938048</v>
+        <v>6938008</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,6 +3624,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411424</v>
+        <v>129411421</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523105</v>
+        <v>523127</v>
       </c>
       <c r="R32" t="n">
-        <v>6938029</v>
+        <v>6938025</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3721,6 +3726,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411393</v>
+        <v>129411430</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523153</v>
+        <v>523138</v>
       </c>
       <c r="R33" t="n">
-        <v>6938019</v>
+        <v>6938048</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3844,32 +3854,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411398</v>
+        <v>129411424</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523124</v>
+        <v>523105</v>
       </c>
       <c r="R34" t="n">
-        <v>6938040</v>
+        <v>6938029</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3915,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3951,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411410</v>
+        <v>129411393</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523076</v>
+        <v>523153</v>
       </c>
       <c r="R35" t="n">
-        <v>6938008</v>
+        <v>6938019</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4017,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4250,7 +4250,7 @@
         <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R41" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R42" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4726,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129411417</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129411406</v>
+        <v>129411427</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523048</v>
+        <v>523103</v>
       </c>
       <c r="R3" t="n">
-        <v>6937993</v>
+        <v>6937994</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411427</v>
+        <v>129411425</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523103</v>
+        <v>523062</v>
       </c>
       <c r="R4" t="n">
-        <v>6937994</v>
+        <v>6938030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411425</v>
+        <v>129411377</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523062</v>
+        <v>523143</v>
       </c>
       <c r="R5" t="n">
-        <v>6938030</v>
+        <v>6938086</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1073,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411377</v>
+        <v>129411395</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523143</v>
+        <v>523103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938086</v>
+        <v>6938056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411395</v>
+        <v>129411406</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523103</v>
+        <v>523048</v>
       </c>
       <c r="R7" t="n">
-        <v>6938056</v>
+        <v>6937993</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växtplats 15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129411380</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129411402</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129411404</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129411420</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129411401</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129411431</v>
+        <v>129411378</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523136</v>
+        <v>523153</v>
       </c>
       <c r="R20" t="n">
-        <v>6938051</v>
+        <v>6938019</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129411408</v>
+        <v>129411431</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523055</v>
+        <v>523136</v>
       </c>
       <c r="R21" t="n">
-        <v>6937994</v>
+        <v>6938051</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2619,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2650,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129411412</v>
+        <v>129411408</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523098</v>
+        <v>523055</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6937994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2725,7 +2720,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växtplats 9</t>
+          <t>Växtplats 13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2747,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129411378</v>
+        <v>129411412</v>
       </c>
       <c r="B23" t="n">
-        <v>80187</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523153</v>
+        <v>523098</v>
       </c>
       <c r="R23" t="n">
-        <v>6938019</v>
+        <v>6937990</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2823,6 +2818,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växtplats 9</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129411415</v>
+        <v>129411376</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>80215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523149</v>
+        <v>523103</v>
       </c>
       <c r="R25" t="n">
-        <v>6938024</v>
+        <v>6938058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3017,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,32 +3043,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411376</v>
+        <v>129411415</v>
       </c>
       <c r="B26" t="n">
-        <v>80215</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523103</v>
+        <v>523149</v>
       </c>
       <c r="R26" t="n">
-        <v>6938058</v>
+        <v>6938024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växtplats 6</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,7 +3148,7 @@
         <v>129411419</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129411418</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129411413</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411398</v>
+        <v>129411421</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523124</v>
+        <v>523127</v>
       </c>
       <c r="R30" t="n">
-        <v>6938040</v>
+        <v>6938025</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växtplats 21</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411410</v>
+        <v>129411430</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523076</v>
+        <v>523138</v>
       </c>
       <c r="R31" t="n">
-        <v>6938008</v>
+        <v>6938048</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3624,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3655,7 +3650,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411421</v>
+        <v>129411424</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3690,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523127</v>
+        <v>523105</v>
       </c>
       <c r="R32" t="n">
-        <v>6938025</v>
+        <v>6938029</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3726,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411430</v>
+        <v>129411393</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523138</v>
+        <v>523153</v>
       </c>
       <c r="R33" t="n">
-        <v>6938048</v>
+        <v>6938019</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3854,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411424</v>
+        <v>129411398</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523105</v>
+        <v>523124</v>
       </c>
       <c r="R34" t="n">
-        <v>6938029</v>
+        <v>6938040</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3925,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411393</v>
+        <v>129411410</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523153</v>
+        <v>523076</v>
       </c>
       <c r="R35" t="n">
-        <v>6938019</v>
+        <v>6938008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4022,6 +4017,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växtplats 11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4250,7 +4250,7 @@
         <v>129411400</v>
       </c>
       <c r="B38" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>129411409</v>
       </c>
       <c r="B39" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>129411399</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411387</v>
+        <v>129411411</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523047</v>
+        <v>523085</v>
       </c>
       <c r="R41" t="n">
-        <v>6937994</v>
+        <v>6937997</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4624,6 +4624,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,32 +4655,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411411</v>
+        <v>129411387</v>
       </c>
       <c r="B42" t="n">
-        <v>98778</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523085</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6937997</v>
+        <v>6937994</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4721,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växtplats 10</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37450-2025 artfynd.xlsx
+++ b/artfynd/A 37450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411423</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411425</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411427</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411429</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411430</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411431</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411377</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411379</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411382</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411383</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411384</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411385</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,6 +2625,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411386</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411387</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411388</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2821,6 +2931,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411389</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2918,6 +3033,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411390</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3015,6 +3135,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411392</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3112,6 +3237,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411393</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3209,6 +3339,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411394</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3306,6 +3441,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411395</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3403,6 +3543,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411396</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3500,6 +3645,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411381</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3597,6 +3747,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411375</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3694,6 +3849,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411376</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3796,6 +3956,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411398</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411399</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4000,6 +4170,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411400</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4102,6 +4277,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411401</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4204,6 +4384,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411402</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411404</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4408,6 +4598,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411406</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4510,6 +4705,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411407</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4612,6 +4812,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411408</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4714,6 +4919,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411409</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4816,6 +5026,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411410</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4918,6 +5133,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411411</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5020,6 +5240,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411412</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5122,6 +5347,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411413</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5224,6 +5454,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411414</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5326,6 +5561,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411415</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5428,6 +5668,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411417</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5530,6 +5775,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411418</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5632,6 +5882,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411419</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5734,6 +5989,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411420</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5831,8 +6091,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411380</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>